--- a/i_test/05_02_test_DANREG_hierarchy/i_input_xls/D3_PERSONS.xlsx
+++ b/i_test/05_02_test_DANREG_hierarchy/i_input_xls/D3_PERSONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_02_test_VID_maxgap_70\i_input_xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Unipi-Unifi\ConcePTIONAlgorithmPregnancies\i_test\05_02_test_DANREG_hierarchy\i_input_xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB89F5E1-F80F-4F30-997C-FFE160B22B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBD7B08-E38F-4441-9193-F9A1B310E9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11775" xr2:uid="{A84A50B3-B156-4398-AD71-353137E1A27F}"/>
+    <workbookView xWindow="-28920" yWindow="525" windowWidth="29040" windowHeight="15720" xr2:uid="{A84A50B3-B156-4398-AD71-353137E1A27F}"/>
   </bookViews>
   <sheets>
     <sheet name="D3_PERSONS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>person_id</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>ConCDM_SIM_200421_00025</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00026</t>
   </si>
 </sst>
 </file>
@@ -929,16 +932,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730889E5-9EA9-4D8A-BD6B-67959545C295}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.21875" customWidth="1"/>
+    <col min="1" max="1" width="46.1796875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" customWidth="1"/>
+    <col min="12" max="12" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -979,7 +982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1000,6 +1003,29 @@
       </c>
       <c r="L2" s="1">
         <v>27285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>1976</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1">
+        <v>28016</v>
       </c>
     </row>
   </sheetData>
